--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -803,25 +803,7 @@
     <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.LRDFN
-Micro.AntibioticSensitivityComment.LRDFN
-Pathology.Autopsy.LRDFN
-Micro.BacteriologyReports.LRDFN
-Pathology.CytoOrganTissueFunction.StaffIEN
-Micro.MicroAntibioticLevel.LRDFN
-Micro.MicroAudit.LRDFN
-Micro.Microbiology.LRDFN
-Micro.MicroOrderedTest.LRDFN
-Micro.MicroSterilityResults.LRDFN
-Micro.MycobacteriologyReports.LRDFN
-Micro.Mycology.LRDFN
-Micro.MycologyReports.LRDFN
-Micro.Parasitology.LRDFN
-Micro.ParasitologyReports.LRDFN
-Micro.ParasitologyStage.LRDFN
-SStaff.SMicroOrderedTest.LRDFN
-Micro.Virology.LRDFN
-Micro.VirologyReports.LRDFN</t>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>DiagnosticReport.encounter</t>
@@ -1564,7 +1546,7 @@
     <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="165.01953125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -247,12 +253,6 @@
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Report
@@ -623,6 +623,9 @@
     <t>open</t>
   </si>
   <si>
+    <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074#LAB</t>
+  </si>
+  <si>
     <t>OBR-24</t>
   </si>
   <si>
@@ -630,9 +633,6 @@
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074#LAB</t>
   </si>
   <si>
     <t>DiagnosticReport.category.id</t>
@@ -716,13 +716,13 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (#60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+  </si>
+  <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (#60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>DiagnosticReport.category:LaboratorySlice</t>
@@ -788,6 +788,12 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
+    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -798,12 +804,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>DiagnosticReport.encounter</t>
@@ -1019,13 +1019,13 @@
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
   </si>
   <si>
+    <t>1437: reference from See mapping for Laboratory Results</t>
+  </si>
+  <si>
     <t>OBXs</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=COMP].target</t>
-  </si>
-  <si>
-    <t>1437: reference from See mapping for Laboratory Results</t>
   </si>
   <si>
     <t>DiagnosticReport.imagingStudy</t>
@@ -1541,12 +1541,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="165.01953125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="165.01953125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="121.93359375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1779,19 +1779,19 @@
         <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2383,13 +2383,13 @@
         <v>82</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>82</v>
@@ -2503,13 +2503,13 @@
         <v>82</v>
       </c>
       <c r="AM8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>82</v>
@@ -2623,13 +2623,13 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>82</v>
@@ -2745,13 +2745,13 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>82</v>
@@ -2861,22 +2861,22 @@
         <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -2983,19 +2983,19 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3101,22 +3101,22 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="14" hidden="true">
@@ -3219,22 +3219,22 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3343,13 +3343,13 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3463,13 +3463,13 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>82</v>
@@ -3582,16 +3582,16 @@
         <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -3701,16 +3701,16 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>82</v>
+        <v>222</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>224</v>
@@ -3826,19 +3826,19 @@
         <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AO19" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP19" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -3943,22 +3943,22 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4185,22 +4185,22 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4307,22 +4307,22 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -4432,19 +4432,19 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4551,22 +4551,22 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -4673,22 +4673,22 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -4798,16 +4798,16 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -4917,16 +4917,16 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>319</v>
@@ -5043,13 +5043,13 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5160,16 +5160,16 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AM30" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5281,13 +5281,13 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5401,13 +5401,13 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5523,13 +5523,13 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5645,13 +5645,13 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -5763,13 +5763,13 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -5880,16 +5880,16 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -5998,16 +5998,16 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6120,16 +6120,16 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Derivation</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file LABORATORY TEST (#60) to us-core-diagnosticreport-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file LABORATORY TEST (60) to us-core-diagnosticreport-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -716,7 +716,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (#60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -788,7 +788,7 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
-    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
@@ -1541,7 +1541,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="165.01953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$42</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="378">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -597,6 +597,127 @@
   </si>
   <si>
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes for diagnostic service sections.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>OBR-24</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:LaboratorySlice</t>
+  </si>
+  <si>
+    <t>LaboratorySlice</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -607,128 +728,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074#LAB</t>
-  </si>
-  <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:LaboratorySlice</t>
-  </si>
-  <si>
-    <t>LaboratorySlice</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -766,6 +766,27 @@
   </si>
   <si>
     <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding</t>
+  </si>
+  <si>
+    <t>1420: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.text</t>
+  </si>
+  <si>
+    <t>1661: source value from LABORATORY TEST - NAME (60-.01)</t>
+  </si>
+  <si>
+    <t>Dim.LabChemTest.LabChemTestName</t>
   </si>
   <si>
     <t>DiagnosticReport.subject</t>
@@ -1503,7 +1524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP38"/>
+  <dimension ref="A1:AP42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.49609375" customWidth="true" bestFit="true"/>
@@ -3167,41 +3188,41 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="T14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X14" t="s" s="2">
+      <c r="Y14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>180</v>
@@ -3219,30 +3240,30 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3265,13 +3286,13 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3322,7 +3343,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3349,7 +3370,7 @@
         <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3357,10 +3378,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3389,7 +3410,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3430,19 +3451,19 @@
         <v>82</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3469,7 +3490,7 @@
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>82</v>
@@ -3477,10 +3498,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3503,19 +3524,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3564,7 +3585,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3588,10 +3609,10 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -3599,10 +3620,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3625,19 +3646,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -3686,7 +3707,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3701,19 +3722,19 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -3721,13 +3742,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>180</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>181</v>
@@ -3769,28 +3790,28 @@
         <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X19" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="T19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X19" t="s" s="2">
+      <c r="Y19" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y19" t="s" s="2">
+      <c r="Z19" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -3823,7 +3844,7 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
@@ -3832,13 +3853,13 @@
         <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -3970,37 +3991,35 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>241</v>
+        <v>195</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>242</v>
+        <v>196</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>243</v>
+        <v>197</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4048,7 +4067,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>239</v>
+        <v>198</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4060,44 +4079,44 @@
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>249</v>
+        <v>199</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>252</v>
+        <v>136</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4106,23 +4125,21 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>253</v>
+        <v>137</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>254</v>
+        <v>138</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>255</v>
+        <v>201</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4158,31 +4175,31 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>251</v>
+        <v>204</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4191,35 +4208,35 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>260</v>
+        <v>199</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>92</v>
@@ -4231,19 +4248,19 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>264</v>
+        <v>206</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>265</v>
+        <v>207</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>267</v>
+        <v>209</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>268</v>
+        <v>210</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4292,49 +4309,49 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>262</v>
+        <v>211</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>271</v>
+        <v>212</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>272</v>
+        <v>213</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4353,19 +4370,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>276</v>
+        <v>195</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>277</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>278</v>
+        <v>216</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>279</v>
+        <v>217</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4414,7 +4431,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4423,47 +4440,47 @@
         <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>282</v>
+        <v>221</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>283</v>
+        <v>222</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>92</v>
@@ -4475,19 +4492,17 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4536,13 +4551,13 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -4551,41 +4566,41 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>292</v>
+        <v>254</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>293</v>
+        <v>255</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>294</v>
+        <v>256</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>295</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -4597,19 +4612,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>298</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>299</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>301</v>
+        <v>263</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4658,13 +4673,13 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -4679,59 +4694,59 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>302</v>
+        <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>295</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>306</v>
+        <v>273</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -4780,16 +4795,16 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
@@ -4801,35 +4816,35 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>92</v>
@@ -4838,22 +4853,22 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -4902,22 +4917,22 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
@@ -4926,25 +4941,25 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4954,27 +4969,29 @@
         <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>323</v>
+        <v>296</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5022,7 +5039,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5043,28 +5060,28 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5083,17 +5100,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5142,7 +5161,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5163,24 +5182,24 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5191,7 +5210,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5203,16 +5222,20 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>197</v>
+        <v>311</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>198</v>
+        <v>312</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5260,19 +5283,19 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>200</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5284,10 +5307,10 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5295,14 +5318,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>136</v>
+        <v>318</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5312,7 +5335,7 @@
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
@@ -5321,18 +5344,20 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>137</v>
+        <v>319</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>138</v>
+        <v>320</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>203</v>
+        <v>321</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5380,7 +5405,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>206</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5392,10 +5417,10 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -5404,10 +5429,10 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>201</v>
+        <v>326</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5415,14 +5440,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5435,26 +5460,24 @@
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>137</v>
+        <v>328</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5502,7 +5525,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5514,7 +5537,7 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5529,7 +5552,7 @@
         <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>134</v>
+        <v>332</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5537,21 +5560,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5560,22 +5583,20 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>197</v>
+        <v>335</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5624,13 +5645,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -5648,10 +5669,10 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -5659,10 +5680,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5670,7 +5691,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>91</v>
@@ -5682,16 +5703,16 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>347</v>
+        <v>195</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>348</v>
+        <v>196</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>349</v>
+        <v>197</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5742,10 +5763,10 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>346</v>
+        <v>198</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>91</v>
@@ -5754,7 +5775,7 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -5769,7 +5790,7 @@
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>350</v>
+        <v>199</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -5777,21 +5798,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>352</v>
+        <v>136</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -5803,18 +5824,18 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>353</v>
+        <v>138</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -5862,19 +5883,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>351</v>
+        <v>204</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -5886,10 +5907,10 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>357</v>
+        <v>199</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -5897,14 +5918,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5917,22 +5938,26 @@
         <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -5956,13 +5981,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -5980,7 +6005,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5992,7 +6017,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6004,10 +6029,10 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>363</v>
+        <v>134</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6015,10 +6040,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6029,7 +6054,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6041,19 +6066,19 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>365</v>
+        <v>195</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6102,13 +6127,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6126,17 +6151,495 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AO38" t="s" s="2">
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AP38" t="s" s="2">
+      <c r="AP41" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP38">
+  <autoFilter ref="A1:AP42">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6146,7 +6649,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI37">
+  <conditionalFormatting sqref="A2:AI41">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -705,7 +705,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="379">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -706,6 +706,9 @@
   </si>
   <si>
     <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+  </si>
+  <si>
+    <t>Dim.LabChemTest.NationalVALabCodeIEN</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -812,7 +815,7 @@
     <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -3725,16 +3728,16 @@
         <v>220</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -3742,13 +3745,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>180</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>181</v>
@@ -3790,7 +3793,7 @@
         <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>82</v>
@@ -3844,7 +3847,7 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
@@ -3864,14 +3867,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3893,13 +3896,13 @@
         <v>182</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3925,13 +3928,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -3949,7 +3952,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>91</v>
@@ -3970,24 +3973,24 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4102,10 +4105,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4222,10 +4225,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4324,10 +4327,10 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>82</v>
@@ -4344,10 +4347,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4446,19 +4449,19 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4466,14 +4469,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4492,17 +4495,17 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4551,7 +4554,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4566,34 +4569,34 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4612,19 +4615,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4673,7 +4676,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4694,28 +4697,28 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4734,19 +4737,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -4795,7 +4798,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4804,7 +4807,7 @@
         <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
@@ -4816,28 +4819,28 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4856,19 +4859,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -4917,7 +4920,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4926,7 +4929,7 @@
         <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
@@ -4941,25 +4944,25 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4978,19 +4981,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5039,7 +5042,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5060,28 +5063,28 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5100,19 +5103,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5161,7 +5164,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5182,24 +5185,24 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5222,19 +5225,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5283,7 +5286,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5307,10 +5310,10 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5318,14 +5321,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5344,19 +5347,19 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5405,7 +5408,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5420,7 +5423,7 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -5429,10 +5432,10 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5440,10 +5443,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5466,16 +5469,16 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5525,7 +5528,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5552,7 +5555,7 @@
         <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5560,14 +5563,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5586,17 +5589,17 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5645,7 +5648,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5669,10 +5672,10 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -5680,10 +5683,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5798,10 +5801,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5918,14 +5921,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5947,10 +5950,10 @@
         <v>137</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>140</v>
@@ -6005,7 +6008,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6040,10 +6043,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6069,16 +6072,16 @@
         <v>195</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6127,7 +6130,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6154,7 +6157,7 @@
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6162,10 +6165,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6188,13 +6191,13 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6245,7 +6248,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6272,7 +6275,7 @@
         <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6280,14 +6283,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6309,14 +6312,14 @@
         <v>195</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6365,7 +6368,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6389,10 +6392,10 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6400,10 +6403,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6429,10 +6432,10 @@
         <v>182</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6462,10 +6465,10 @@
         <v>186</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6483,7 +6486,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6507,10 +6510,10 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6518,10 +6521,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6544,19 +6547,19 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6605,7 +6608,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6629,10 +6632,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="423">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -781,6 +781,139 @@
   </si>
   <si>
     <t>1420: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1420-2: fixed value = http://loinc.org</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1420-1: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>1420-3: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>DiagnosticReport.code.text</t>
@@ -1527,11 +1660,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP42"/>
+  <dimension ref="A1:AP49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.49609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.37890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="41.1328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.1328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="15.34765625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -4364,29 +4497,25 @@
         <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>195</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4434,7 +4563,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4446,22 +4575,22 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4469,44 +4598,44 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>248</v>
+        <v>136</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>249</v>
+        <v>137</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>138</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4542,61 +4671,61 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>257</v>
+        <v>199</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4606,7 +4735,7 @@
         <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>82</v>
@@ -4615,19 +4744,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>261</v>
+        <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4637,7 +4766,7 @@
         <v>82</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>82</v>
@@ -4676,7 +4805,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4691,34 +4820,34 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4728,7 +4857,7 @@
         <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -4737,20 +4866,18 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>272</v>
+        <v>195</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -4798,7 +4925,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4807,7 +4934,7 @@
         <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
@@ -4819,28 +4946,28 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4859,19 +4986,17 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>284</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -4920,7 +5045,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4929,47 +5054,47 @@
         <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>92</v>
@@ -4981,19 +5106,17 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>295</v>
+        <v>195</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5042,13 +5165,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5057,41 +5180,41 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5103,19 +5226,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>309</v>
+        <v>283</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5164,13 +5287,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5185,24 +5308,24 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5213,31 +5336,31 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>313</v>
+        <v>215</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>314</v>
+        <v>216</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>315</v>
+        <v>217</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>316</v>
+        <v>218</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5286,13 +5409,13 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>219</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
@@ -5301,19 +5424,19 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>317</v>
+        <v>222</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5321,21 +5444,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>319</v>
+        <v>292</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>92</v>
@@ -5344,22 +5467,20 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5408,13 +5529,13 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -5423,41 +5544,41 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5466,21 +5587,23 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5528,13 +5651,13 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -5549,38 +5672,38 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -5589,17 +5712,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5648,16 +5773,16 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>103</v>
@@ -5669,28 +5794,28 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5700,25 +5825,29 @@
         <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>195</v>
+        <v>328</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>196</v>
+        <v>329</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -5766,7 +5895,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>198</v>
+        <v>326</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5775,10 +5904,10 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -5790,25 +5919,25 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>199</v>
+        <v>335</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>136</v>
+        <v>338</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5818,27 +5947,29 @@
         <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>137</v>
+        <v>339</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>138</v>
+        <v>340</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>201</v>
+        <v>341</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -5886,7 +6017,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>204</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5898,7 +6029,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -5907,28 +6038,28 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>199</v>
+        <v>346</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5941,25 +6072,25 @@
         <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>137</v>
+        <v>350</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>140</v>
+        <v>353</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>146</v>
+        <v>343</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6008,7 +6139,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6020,7 +6151,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6029,24 +6160,24 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>134</v>
+        <v>346</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6057,7 +6188,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6069,19 +6200,19 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>195</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6130,13 +6261,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6154,10 +6285,10 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>353</v>
+        <v>301</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6165,42 +6296,46 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6248,13 +6383,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6263,7 +6398,7 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
@@ -6272,10 +6407,10 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6283,21 +6418,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6309,18 +6444,18 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>195</v>
+        <v>373</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6368,13 +6503,13 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
@@ -6392,10 +6527,10 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6403,14 +6538,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6426,19 +6561,21 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>182</v>
+        <v>380</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6462,13 +6599,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6486,7 +6623,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6510,7 +6647,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>371</v>
@@ -6521,10 +6658,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6535,7 +6672,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6547,20 +6684,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>373</v>
+        <v>195</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>196</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -6608,41 +6741,883 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>198</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AP42" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
+      <c r="H43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AK45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP42">
+  <autoFilter ref="A1:AP49">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6652,7 +7627,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI41">
+  <conditionalFormatting sqref="A2:AI48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
